--- a/data/trans_camb/IP16B06-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16B06-Estudios-trans_camb.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-79,78; 0,0</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,78; 0,0</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-78,5; 0,0</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-60,45; 0,0</t>
+          <t>-55,33; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-78,5; 0,0</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-60,45; 0,0</t>
+          <t>-55,33; 0,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">

--- a/data/trans_camb/IP16B06-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16B06-Estudios-trans_camb.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-79,78; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-79,78; 0,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-78,5; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-55,33; 0,0</t>
+          <t>-54,22; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-78,5; 0,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-55,33; 0,0</t>
+          <t>-54,22; 0,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
